--- a/Assets/Resources/story/1.xlsx
+++ b/Assets/Resources/story/1.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>名字</t>
   </si>
@@ -49,28 +49,58 @@
     <t>背景音乐</t>
   </si>
   <si>
+    <t>动作1</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>动作图片1</t>
+  </si>
+  <si>
+    <t>动作2</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>动作图片2</t>
+  </si>
+  <si>
     <t>张三</t>
   </si>
   <si>
     <t>你好</t>
   </si>
   <si>
+    <t>appearAt</t>
+  </si>
+  <si>
     <t>李四</t>
   </si>
   <si>
     <t>我不好</t>
   </si>
   <si>
-    <t>zs</t>
+    <t>disappear</t>
   </si>
   <si>
     <t>why?</t>
   </si>
   <si>
-    <t>ls</t>
+    <t>moveTo</t>
   </si>
   <si>
     <t>guess</t>
+  </si>
+  <si>
+    <t>choice</t>
+  </si>
+  <si>
+    <t>choice1</t>
+  </si>
+  <si>
+    <t>choice2</t>
   </si>
 </sst>
 </file>
@@ -1001,10 +1031,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1023,40 +1053,141 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2">
+        <v>-100</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4">
+        <v>50</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/story/1.xlsx
+++ b/Assets/Resources/story/1.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="24">
   <si>
     <t>名字</t>
   </si>
@@ -1031,8 +1031,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
@@ -1175,18 +1175,523 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>-100</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8">
+        <v>50</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10">
+        <v>-100</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12">
+        <v>50</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <v>-100</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16">
+        <v>50</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18">
+        <v>-100</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20">
+        <v>50</v>
+      </c>
+      <c r="L20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>14</v>
+      </c>
+      <c r="K22">
+        <v>-100</v>
+      </c>
+      <c r="L22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24">
+        <v>50</v>
+      </c>
+      <c r="L24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B26" t="s">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>23</v>
       </c>
-      <c r="E6">
+      <c r="E26">
         <v>3</v>
       </c>
     </row>
